--- a/public/template/training-attendance/crm/booking.xlsx
+++ b/public/template/training-attendance/crm/booking.xlsx
@@ -1,229 +1,340 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\培训 - 副本\CRM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>南货航</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>开班第X期CRM培训名单（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>广州壹泉湾温泉</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>酒店）</t>
+    </r>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>公司</t>
+  </si>
+  <si>
+    <t>培训班期</t>
+  </si>
+  <si>
+    <t>开始日期</t>
+  </si>
+  <si>
+    <t>结束日期</t>
+  </si>
+  <si>
+    <t>姓名</t>
+  </si>
+  <si>
+    <t>员工号</t>
+  </si>
+  <si>
+    <t>技术等级</t>
+  </si>
+  <si>
+    <t>机型</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>教员</t>
+  </si>
+  <si>
+    <t>南货航飞行部</t>
+  </si>
+  <si>
+    <t>第X期</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="28">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color rgb="FFFF0000"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -523,194 +634,194 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="49">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -958,7 +1069,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -967,7 +1078,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -980,74 +1091,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1299,180 +1347,533 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.72727272727273" defaultRowHeight="17.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K38"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="17.5"/>
   <cols>
-    <col width="9.13636363636364" customWidth="1" style="1" min="1" max="1"/>
-    <col width="21.6272727272727" customWidth="1" style="1" min="2" max="2"/>
-    <col width="10.1272727272727" customWidth="1" style="1" min="3" max="3"/>
-    <col width="12.6363636363636" customWidth="1" style="1" min="4" max="5"/>
-    <col width="12.6363636363636" customWidth="1" style="2" min="6" max="7"/>
-    <col width="30.6272727272727" customWidth="1" style="1" min="8" max="8"/>
-    <col width="12.6363636363636" customWidth="1" style="1" min="9" max="10"/>
-    <col width="13.7545454545455" customWidth="1" style="1" min="11" max="11"/>
-    <col width="8.72727272727273" customWidth="1" style="1" min="12" max="16384"/>
+    <col min="1" max="1" width="9.13636363636364" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.6272727272727" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1272727272727" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.6363636363636" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.6363636363636" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30.6272727272727" style="1" customWidth="1"/>
+    <col min="9" max="10" width="12.6363636363636" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7545454545455" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>南货航开班第X期CRM培训名单（广州壹泉湾温泉酒店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>公司</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>培训班期</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>开始日期</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>结束日期</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>员工号</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>技术等级</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>机型</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="K2" s="7" t="inlineStr">
-        <is>
-          <t>教员</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="1">
-      <c r="A3" s="8" t="n">
+    <row r="1" s="1" customFormat="1" ht="26" customHeight="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:11">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>南货航飞行部</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>第X期</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n">
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:11">
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11">
         <v>777</v>
       </c>
-      <c r="J3" s="7" t="n"/>
-      <c r="K3" s="7" t="n"/>
-    </row>
-    <row r="4" customFormat="1" s="1">
-      <c r="A4" s="8" t="n">
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:11">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>南货航飞行部</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>第X期</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="11" t="n">
+      <c r="B4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11">
         <v>777</v>
       </c>
-      <c r="J4" s="7" t="n"/>
-    </row>
-    <row r="5" customFormat="1" s="1"/>
-    <row r="6" customFormat="1" s="1"/>
-    <row r="7" customFormat="1" s="1"/>
-    <row r="8" customFormat="1" s="1"/>
-    <row r="9" customFormat="1" s="1"/>
-    <row r="10" customFormat="1" s="1"/>
-    <row r="11" customFormat="1" s="1"/>
-    <row r="12" customFormat="1" s="1"/>
-    <row r="13" customFormat="1" s="1"/>
-    <row r="14" customFormat="1" s="1"/>
-    <row r="15" customFormat="1" s="1"/>
-    <row r="16" customFormat="1" s="1"/>
-    <row r="17" customFormat="1" s="1"/>
-    <row r="18" customFormat="1" s="1"/>
-    <row r="19" customFormat="1" s="1"/>
-    <row r="20" customFormat="1" s="1"/>
-    <row r="21" customFormat="1" s="1"/>
-    <row r="22" customFormat="1" s="1"/>
-    <row r="23" customFormat="1" s="1"/>
-    <row r="24" customFormat="1" s="1"/>
-    <row r="25" customFormat="1" s="1"/>
-    <row r="26" customFormat="1" s="1"/>
-    <row r="27" customFormat="1" s="1"/>
-    <row r="28" customFormat="1" s="1"/>
-    <row r="29" customFormat="1" s="1"/>
-    <row r="30" customFormat="1" s="1"/>
-    <row r="31" customFormat="1" s="1"/>
-    <row r="32" customFormat="1" s="1"/>
-    <row r="33" customFormat="1" s="1"/>
-    <row r="34" customFormat="1" s="1"/>
-    <row r="35" customFormat="1" s="1"/>
-    <row r="36" customFormat="1" s="1"/>
-    <row r="37" customFormat="1" s="1"/>
+      <c r="J4" s="7"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:11">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="7"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:11">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:11">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="7"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:11">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:11">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:11">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="7"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:11">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:11">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:11">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:11">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="7"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:11">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="7"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:11">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:10">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="7"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:10">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="7"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:10">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="7"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:10">
+      <c r="A20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="7"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:10">
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="7"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:10">
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="7"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:10">
+      <c r="A23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="7"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:10">
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="7"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:10">
+      <c r="A25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="7"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:10">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="7"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:10">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="7"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:10">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="7"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:10">
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="7"/>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:10">
+      <c r="A30" s="8"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="7"/>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:10">
+      <c r="A31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="7"/>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:10">
+      <c r="A32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="7"/>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:10">
+      <c r="A33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="7"/>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:10">
+      <c r="A34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="7"/>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:10">
+      <c r="A35" s="8"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="7"/>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:10">
+      <c r="A36" s="8"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="7"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:10">
+      <c r="A37" s="8"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="7"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="8"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"机长,副驾驶"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="H2" listDataValidation="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>